--- a/uploads/607260013/607260013.xlsx
+++ b/uploads/607260013/607260013.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -121,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -147,10 +146,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -165,7 +164,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -174,11 +173,23 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -545,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -744,7 +755,7 @@
           <t>DateOfArrival</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="20" t="n">
         <v>46448</v>
       </c>
     </row>
@@ -759,7 +770,7 @@
           <t>DateOfDeparture</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="21" t="n">
         <v>46463</v>
       </c>
     </row>
@@ -774,7 +785,7 @@
           <t>StartDate</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="20" t="n">
         <v>46448</v>
       </c>
     </row>
@@ -789,7 +800,7 @@
           <t>EndDate</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="21" t="n">
         <v>46463</v>
       </c>
     </row>
@@ -932,6 +943,36 @@
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Quotations ID</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Quotations_id</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>9311</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Itineraries ID</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>itineraries_id</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9348</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1008,7 +1049,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="22" t="n">
         <v>46448</v>
       </c>
       <c r="D5" s="14" t="inlineStr">
@@ -1031,7 +1072,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="23" t="n">
         <v>46449</v>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -1054,7 +1095,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="22" t="n">
         <v>46450</v>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -1077,7 +1118,7 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="23" t="n">
         <v>46451</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -1100,7 +1141,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="22" t="n">
         <v>46452</v>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -1123,7 +1164,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="23" t="n">
         <v>46453</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -1146,7 +1187,7 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="22" t="n">
         <v>46454</v>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -1169,7 +1210,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="23" t="n">
         <v>46455</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -1192,7 +1233,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="22" t="n">
         <v>46456</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -1215,7 +1256,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="23" t="n">
         <v>46457</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -1238,7 +1279,7 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="22" t="n">
         <v>46458</v>
       </c>
       <c r="D15" s="14" t="inlineStr">
@@ -1261,7 +1302,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="23" t="n">
         <v>46459</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -1284,7 +1325,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="22" t="n">
         <v>46460</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -1307,7 +1348,7 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="C18" s="18" t="n">
+      <c r="C18" s="23" t="n">
         <v>46461</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
@@ -1330,7 +1371,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="22" t="n">
         <v>46462</v>
       </c>
       <c r="D19" s="14" t="inlineStr">
@@ -1353,7 +1394,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C20" s="18" t="n">
+      <c r="C20" s="23" t="n">
         <v>46463</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
